--- a/Results_experiment/exp_2/preds_3364444555550000.xlsx
+++ b/Results_experiment/exp_2/preds_3364444555550000.xlsx
@@ -1443,7 +1443,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D2">
-        <v>0.4910063445568085</v>
+        <v>0.2279306352138519</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1457,7 +1457,7 @@
         <v>12.30000019073486</v>
       </c>
       <c r="D3">
-        <v>9.41541862487793</v>
+        <v>9.671874046325684</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1471,7 +1471,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D4">
-        <v>1.400646090507507</v>
+        <v>0.6162348985671997</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1485,7 +1485,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D5">
-        <v>1.146547079086304</v>
+        <v>3.015079498291016</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1499,7 +1499,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D6">
-        <v>-2.646042346954346</v>
+        <v>-1.587782502174377</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1513,7 +1513,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D7">
-        <v>-3.201912879943848</v>
+        <v>-2.961880445480347</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1527,7 +1527,7 @@
         <v>-18</v>
       </c>
       <c r="D8">
-        <v>-1.0075443983078</v>
+        <v>0.3717504441738129</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1541,7 +1541,7 @@
         <v>-33.70000076293945</v>
       </c>
       <c r="D9">
-        <v>-18.4994068145752</v>
+        <v>-21.34970283508301</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1555,7 +1555,7 @@
         <v>-24.39999961853027</v>
       </c>
       <c r="D10">
-        <v>-12.7086296081543</v>
+        <v>-13.66551208496094</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1569,7 +1569,7 @@
         <v>-12</v>
       </c>
       <c r="D11">
-        <v>-5.977518081665039</v>
+        <v>-6.766227245330811</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1583,7 +1583,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D12">
-        <v>-2.39842677116394</v>
+        <v>-2.873685121536255</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1597,7 +1597,7 @@
         <v>-19.60000038146973</v>
       </c>
       <c r="D13">
-        <v>-14.31324768066406</v>
+        <v>-15.96002006530762</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1611,7 +1611,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D14">
-        <v>-0.2250508368015289</v>
+        <v>-1.245120525360107</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1625,7 +1625,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D15">
-        <v>-0.8092045187950134</v>
+        <v>-0.5852020978927612</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1639,7 +1639,7 @@
         <v>20.60000038146973</v>
       </c>
       <c r="D16">
-        <v>5.531577587127686</v>
+        <v>4.80702543258667</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1653,7 +1653,7 @@
         <v>-9.5</v>
       </c>
       <c r="D17">
-        <v>-5.219351768493652</v>
+        <v>-5.878961086273193</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1667,7 +1667,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D18">
-        <v>12.40945434570312</v>
+        <v>12.75769805908203</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1681,7 +1681,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D19">
-        <v>-0.09210363030433655</v>
+        <v>0.3004062473773956</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1695,7 +1695,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D20">
-        <v>0.1755640208721161</v>
+        <v>-3.925939798355103</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1709,7 +1709,7 @@
         <v>-14</v>
       </c>
       <c r="D21">
-        <v>-11.32228469848633</v>
+        <v>-10.38572406768799</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1723,7 +1723,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D22">
-        <v>0.992131233215332</v>
+        <v>1.700920224189758</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1737,7 +1737,7 @@
         <v>-12.39999961853027</v>
       </c>
       <c r="D23">
-        <v>-10.45694160461426</v>
+        <v>-9.424178123474121</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1751,7 +1751,7 @@
         <v>-13.69999980926514</v>
       </c>
       <c r="D24">
-        <v>-7.521090507507324</v>
+        <v>-10.54681873321533</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1765,7 +1765,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D25">
-        <v>1.841338634490967</v>
+        <v>2.374742269515991</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1779,7 +1779,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D26">
-        <v>0.9764844179153442</v>
+        <v>1.069176197052002</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1793,7 +1793,7 @@
         <v>3</v>
       </c>
       <c r="D27">
-        <v>-3.719944715499878</v>
+        <v>-7.60097074508667</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1807,7 +1807,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D28">
-        <v>-0.9837570190429688</v>
+        <v>-2.519142150878906</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1821,7 +1821,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D29">
-        <v>-3.706400156021118</v>
+        <v>-4.758203983306885</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1835,7 +1835,7 @@
         <v>-18.79999923706055</v>
       </c>
       <c r="D30">
-        <v>-8.605356216430664</v>
+        <v>-11.39387989044189</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1849,7 +1849,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D31">
-        <v>-0.03888261318206787</v>
+        <v>0.007596224546432495</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1863,7 +1863,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D32">
-        <v>3.19273829460144</v>
+        <v>3.512356519699097</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1877,7 +1877,7 @@
         <v>-23.10000038146973</v>
       </c>
       <c r="D33">
-        <v>-13.92313098907471</v>
+        <v>-16.42811584472656</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1891,7 +1891,7 @@
         <v>-19.39999961853027</v>
       </c>
       <c r="D34">
-        <v>-17.2331428527832</v>
+        <v>-19.5233039855957</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1905,7 +1905,7 @@
         <v>-9.5</v>
       </c>
       <c r="D35">
-        <v>-2.48149585723877</v>
+        <v>-5.571846008300781</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1919,7 +1919,7 @@
         <v>-1.5</v>
       </c>
       <c r="D36">
-        <v>-7.151492118835449</v>
+        <v>-0.5094701647758484</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1933,7 +1933,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D37">
-        <v>-3.875327348709106</v>
+        <v>-4.240118980407715</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1947,7 +1947,7 @@
         <v>-5.5</v>
       </c>
       <c r="D38">
-        <v>-4.289291381835938</v>
+        <v>-7.898543834686279</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1961,7 +1961,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D39">
-        <v>2.101272821426392</v>
+        <v>1.391190528869629</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1975,7 +1975,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D40">
-        <v>3.579403638839722</v>
+        <v>3.822211027145386</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1989,7 +1989,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D41">
-        <v>-3.647187471389771</v>
+        <v>-4.3880615234375</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2003,7 +2003,7 @@
         <v>-16.70000076293945</v>
       </c>
       <c r="D42">
-        <v>-12.74267864227295</v>
+        <v>-10.48996257781982</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2017,7 +2017,7 @@
         <v>-3.5</v>
       </c>
       <c r="D43">
-        <v>-0.06283462047576904</v>
+        <v>-0.1527349054813385</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2031,7 +2031,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D44">
-        <v>0.9974937438964844</v>
+        <v>1.272774577140808</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2045,7 +2045,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D45">
-        <v>-10.33847999572754</v>
+        <v>-8.343306541442871</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2059,7 +2059,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D46">
-        <v>1.894625902175903</v>
+        <v>1.499846577644348</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2073,7 +2073,7 @@
         <v>-3.5</v>
       </c>
       <c r="D47">
-        <v>0.5741516351699829</v>
+        <v>-0.07148098945617676</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2087,7 +2087,7 @@
         <v>-12.19999980926514</v>
       </c>
       <c r="D48">
-        <v>-2.774559259414673</v>
+        <v>-2.458633184432983</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2101,7 +2101,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D49">
-        <v>-5.687644004821777</v>
+        <v>-4.516757488250732</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2115,7 +2115,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D50">
-        <v>-1.089136958122253</v>
+        <v>1.592056393623352</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2129,7 +2129,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D51">
-        <v>4.605432510375977</v>
+        <v>4.426994800567627</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2143,7 +2143,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D52">
-        <v>-1.788836121559143</v>
+        <v>-3.458758592605591</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2157,7 +2157,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D53">
-        <v>-0.9657739400863647</v>
+        <v>-0.8185674548149109</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2171,7 +2171,7 @@
         <v>-13.30000019073486</v>
       </c>
       <c r="D54">
-        <v>-10.30438613891602</v>
+        <v>-11.5743236541748</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2185,7 +2185,7 @@
         <v>3.5</v>
       </c>
       <c r="D55">
-        <v>-0.009488016366958618</v>
+        <v>1.307895183563232</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2199,7 +2199,7 @@
         <v>-20.20000076293945</v>
       </c>
       <c r="D56">
-        <v>-16.72606086730957</v>
+        <v>-17.03075408935547</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2213,7 +2213,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D57">
-        <v>-0.9897327423095703</v>
+        <v>-1.940341353416443</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2227,7 +2227,7 @@
         <v>-9.600000381469727</v>
       </c>
       <c r="D58">
-        <v>-7.605602264404297</v>
+        <v>-5.833329677581787</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2241,7 +2241,7 @@
         <v>29.79999923706055</v>
       </c>
       <c r="D59">
-        <v>14.8190746307373</v>
+        <v>14.90780735015869</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2255,7 +2255,7 @@
         <v>-13.19999980926514</v>
       </c>
       <c r="D60">
-        <v>-6.923996925354004</v>
+        <v>-5.8461594581604</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2269,7 +2269,7 @@
         <v>-5.800000190734863</v>
       </c>
       <c r="D61">
-        <v>3.320753812789917</v>
+        <v>0.2259598076343536</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2283,7 +2283,7 @@
         <v>-16.10000038146973</v>
       </c>
       <c r="D62">
-        <v>-4.882240772247314</v>
+        <v>-4.441015720367432</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2297,7 +2297,7 @@
         <v>-1</v>
       </c>
       <c r="D63">
-        <v>-1.019978761672974</v>
+        <v>-1.555993437767029</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2311,7 +2311,7 @@
         <v>-17.39999961853027</v>
       </c>
       <c r="D64">
-        <v>-7.731088638305664</v>
+        <v>-8.027002334594727</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2325,7 +2325,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D65">
-        <v>0.2531599104404449</v>
+        <v>0.4368265569210052</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2339,7 +2339,7 @@
         <v>-14.80000019073486</v>
       </c>
       <c r="D66">
-        <v>-11.12950420379639</v>
+        <v>-9.953166007995605</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2353,7 +2353,7 @@
         <v>5</v>
       </c>
       <c r="D67">
-        <v>0.7137192487716675</v>
+        <v>2.550136566162109</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2367,7 +2367,7 @@
         <v>-19.79999923706055</v>
       </c>
       <c r="D68">
-        <v>-14.10917091369629</v>
+        <v>-16.54770851135254</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2381,7 +2381,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D69">
-        <v>-1.305566906929016</v>
+        <v>-0.08375677466392517</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2395,7 +2395,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D70">
-        <v>-2.623935461044312</v>
+        <v>-3.806367635726929</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2409,7 +2409,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D71">
-        <v>-8.239224433898926</v>
+        <v>-9.975082397460938</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2423,7 +2423,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D72">
-        <v>5.676511764526367</v>
+        <v>5.836167335510254</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2437,7 +2437,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D73">
-        <v>-1.046995043754578</v>
+        <v>-2.565342426300049</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2451,7 +2451,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="D74">
-        <v>8.450677871704102</v>
+        <v>7.660336017608643</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2465,7 +2465,7 @@
         <v>-9.199999809265137</v>
       </c>
       <c r="D75">
-        <v>-6.260424137115479</v>
+        <v>-4.272465705871582</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2479,7 +2479,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D76">
-        <v>-1.693153858184814</v>
+        <v>-3.928778648376465</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2493,7 +2493,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D77">
-        <v>0.2437928020954132</v>
+        <v>0.3043020665645599</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2507,7 +2507,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D78">
-        <v>-4.512746334075928</v>
+        <v>-3.704099655151367</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2521,7 +2521,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D79">
-        <v>-0.2694835662841797</v>
+        <v>-0.366215854883194</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2535,7 +2535,7 @@
         <v>-11.30000019073486</v>
       </c>
       <c r="D80">
-        <v>-9.100963592529297</v>
+        <v>-9.104654312133789</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2549,7 +2549,7 @@
         <v>-21.29999923706055</v>
       </c>
       <c r="D81">
-        <v>-5.404287815093994</v>
+        <v>-4.711759090423584</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2563,7 +2563,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D82">
-        <v>7.174471378326416</v>
+        <v>6.486214160919189</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2577,7 +2577,7 @@
         <v>-10.39999961853027</v>
       </c>
       <c r="D83">
-        <v>-5.180261135101318</v>
+        <v>-4.904098033905029</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2591,7 +2591,7 @@
         <v>-20.39999961853027</v>
       </c>
       <c r="D84">
-        <v>-17.37667274475098</v>
+        <v>-18.34157180786133</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2605,7 +2605,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D85">
-        <v>-0.3872573673725128</v>
+        <v>-0.4843490123748779</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2619,7 +2619,7 @@
         <v>-8.399999618530273</v>
       </c>
       <c r="D86">
-        <v>-5.279898643493652</v>
+        <v>-6.089135646820068</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2633,7 +2633,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D87">
-        <v>-4.919585227966309</v>
+        <v>2.302281618118286</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2647,7 +2647,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D88">
-        <v>-6.283694267272949</v>
+        <v>-6.533870697021484</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2661,7 +2661,7 @@
         <v>11.69999980926514</v>
       </c>
       <c r="D89">
-        <v>13.07211685180664</v>
+        <v>12.14143371582031</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2675,7 +2675,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D90">
-        <v>3.064651727676392</v>
+        <v>4.054150104522705</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2689,7 +2689,7 @@
         <v>13.69999980926514</v>
       </c>
       <c r="D91">
-        <v>4.100086212158203</v>
+        <v>3.459599733352661</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2703,7 +2703,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D92">
-        <v>-5.280028343200684</v>
+        <v>-7.543626308441162</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2717,7 +2717,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D93">
-        <v>-0.62230384349823</v>
+        <v>0.8583015203475952</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2731,7 +2731,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D94">
-        <v>1.666213512420654</v>
+        <v>1.171590447425842</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2745,7 +2745,7 @@
         <v>-5.5</v>
       </c>
       <c r="D95">
-        <v>-3.710015535354614</v>
+        <v>-4.656728744506836</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2759,7 +2759,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D96">
-        <v>-0.7391935586929321</v>
+        <v>-0.6147938966751099</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2773,7 +2773,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>0.3146074712276459</v>
+        <v>1.16576611995697</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2787,7 +2787,7 @@
         <v>6</v>
       </c>
       <c r="D98">
-        <v>1.456539750099182</v>
+        <v>1.971822619438171</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2801,7 +2801,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D99">
-        <v>-1.402642726898193</v>
+        <v>-1.003911137580872</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2815,7 +2815,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D100">
-        <v>-5.450736045837402</v>
+        <v>-4.662915706634521</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2829,7 +2829,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D101">
-        <v>0.63789963722229</v>
+        <v>2.598192691802979</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2843,7 +2843,7 @@
         <v>-7.199999809265137</v>
       </c>
       <c r="D102">
-        <v>-1.978275537490845</v>
+        <v>-1.941673278808594</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2857,7 +2857,7 @@
         <v>21.89999961853027</v>
       </c>
       <c r="D103">
-        <v>13.83512115478516</v>
+        <v>15.664626121521</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2871,7 +2871,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D104">
-        <v>0.4506652057170868</v>
+        <v>1.386462330818176</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2885,7 +2885,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D105">
-        <v>0.6965150833129883</v>
+        <v>0.5522431135177612</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2899,7 +2899,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D106">
-        <v>3.21490740776062</v>
+        <v>3.240662813186646</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2913,7 +2913,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D107">
-        <v>-0.2947226464748383</v>
+        <v>-0.01238545775413513</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2927,7 +2927,7 @@
         <v>-19</v>
       </c>
       <c r="D108">
-        <v>-15.39648628234863</v>
+        <v>-16.37843894958496</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2941,7 +2941,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D109">
-        <v>-1.807794570922852</v>
+        <v>-3.449008703231812</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2955,7 +2955,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D110">
-        <v>-6.978643417358398</v>
+        <v>-7.6552734375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2969,7 +2969,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D111">
-        <v>-3.520205736160278</v>
+        <v>-4.123079299926758</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2983,7 +2983,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D112">
-        <v>0.2010110318660736</v>
+        <v>1.20560610294342</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2997,7 +2997,7 @@
         <v>1.5</v>
       </c>
       <c r="D113">
-        <v>0.3326073586940765</v>
+        <v>-0.008373826742172241</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3011,7 +3011,7 @@
         <v>4</v>
       </c>
       <c r="D114">
-        <v>0.1737001836299896</v>
+        <v>-0.9308085441589355</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3025,7 +3025,7 @@
         <v>-11.60000038146973</v>
       </c>
       <c r="D115">
-        <v>-3.385304689407349</v>
+        <v>-3.450959205627441</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3039,7 +3039,7 @@
         <v>-13.5</v>
       </c>
       <c r="D116">
-        <v>-10.29306030273438</v>
+        <v>-9.12647533416748</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3053,7 +3053,7 @@
         <v>-14</v>
       </c>
       <c r="D117">
-        <v>-8.596034049987793</v>
+        <v>-9.247786521911621</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3067,7 +3067,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D118">
-        <v>2.988367795944214</v>
+        <v>4.029028415679932</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3081,7 +3081,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D119">
-        <v>1.126475214958191</v>
+        <v>0.9748610258102417</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3095,7 +3095,7 @@
         <v>-7.099999904632568</v>
       </c>
       <c r="D120">
-        <v>-1.073365688323975</v>
+        <v>1.103414177894592</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3109,7 +3109,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D121">
-        <v>0.3882745206356049</v>
+        <v>1.585168957710266</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3123,7 +3123,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D122">
-        <v>3.028361082077026</v>
+        <v>3.073936462402344</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3137,7 +3137,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D123">
-        <v>-0.9230213165283203</v>
+        <v>-0.6921404600143433</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3151,7 +3151,7 @@
         <v>-17.39999961853027</v>
       </c>
       <c r="D124">
-        <v>-14.55419635772705</v>
+        <v>-16.37435150146484</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3165,7 +3165,7 @@
         <v>-10.60000038146973</v>
       </c>
       <c r="D125">
-        <v>-11.88174057006836</v>
+        <v>-12.08797073364258</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3179,7 +3179,7 @@
         <v>14.89999961853027</v>
       </c>
       <c r="D126">
-        <v>11.42933464050293</v>
+        <v>12.25772190093994</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3193,7 +3193,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D127">
-        <v>4.308379173278809</v>
+        <v>4.435592651367188</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3207,7 +3207,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D128">
-        <v>0.1269111335277557</v>
+        <v>0.429988294839859</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3221,7 +3221,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D129">
-        <v>0.2442599833011627</v>
+        <v>0.1187612116336823</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3235,7 +3235,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D130">
-        <v>-2.30796217918396</v>
+        <v>-1.903708934783936</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3249,7 +3249,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D131">
-        <v>-1.252917170524597</v>
+        <v>-1.818905234336853</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3263,7 +3263,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D132">
-        <v>-5.009014129638672</v>
+        <v>-5.375748157501221</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3277,7 +3277,7 @@
         <v>-19.70000076293945</v>
       </c>
       <c r="D133">
-        <v>-15.80665588378906</v>
+        <v>-15.78106784820557</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3291,7 +3291,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D134">
-        <v>-2.655145406723022</v>
+        <v>-2.807126760482788</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3305,7 +3305,7 @@
         <v>-10</v>
       </c>
       <c r="D135">
-        <v>-3.471670150756836</v>
+        <v>-4.870766162872314</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3319,7 +3319,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D136">
-        <v>0.2718051373958588</v>
+        <v>0.1405780017375946</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3333,7 +3333,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D137">
-        <v>-2.549299001693726</v>
+        <v>-2.259559392929077</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3347,7 +3347,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D138">
-        <v>1.194288492202759</v>
+        <v>2.601134538650513</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3361,7 +3361,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D139">
-        <v>-1.853472471237183</v>
+        <v>-3.811128854751587</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3375,7 +3375,7 @@
         <v>-8.399999618530273</v>
       </c>
       <c r="D140">
-        <v>-4.51387882232666</v>
+        <v>-4.08177661895752</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3389,7 +3389,7 @@
         <v>12.89999961853027</v>
       </c>
       <c r="D141">
-        <v>-0.06413474678993225</v>
+        <v>0.4038391411304474</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3403,7 +3403,7 @@
         <v>-21.20000076293945</v>
       </c>
       <c r="D142">
-        <v>-7.486529350280762</v>
+        <v>-6.172366619110107</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3417,7 +3417,7 @@
         <v>2.5</v>
       </c>
       <c r="D143">
-        <v>0.2135526835918427</v>
+        <v>-0.2993643581867218</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3431,7 +3431,7 @@
         <v>-25.89999961853027</v>
       </c>
       <c r="D144">
-        <v>-7.056406021118164</v>
+        <v>-12.48759269714355</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3445,7 +3445,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D145">
-        <v>1.948984146118164</v>
+        <v>0.4899093806743622</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3459,7 +3459,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D146">
-        <v>1.686611413955688</v>
+        <v>1.864145398139954</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3473,7 +3473,7 @@
         <v>-19.29999923706055</v>
       </c>
       <c r="D147">
-        <v>-7.328912258148193</v>
+        <v>-7.289759159088135</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3487,7 +3487,7 @@
         <v>-8.899999618530273</v>
       </c>
       <c r="D148">
-        <v>-5.053196907043457</v>
+        <v>-4.302999019622803</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3501,7 +3501,7 @@
         <v>-10</v>
       </c>
       <c r="D149">
-        <v>-7.286184310913086</v>
+        <v>-10.26066398620605</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3515,7 +3515,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D150">
-        <v>-6.830013275146484</v>
+        <v>-8.287225723266602</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3529,7 +3529,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D151">
-        <v>2.116315364837646</v>
+        <v>2.160338163375854</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3543,7 +3543,7 @@
         <v>-4.5</v>
       </c>
       <c r="D152">
-        <v>0.6393373012542725</v>
+        <v>1.087933421134949</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3557,7 +3557,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D153">
-        <v>0.08508729934692383</v>
+        <v>0.0787215530872345</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3571,7 +3571,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D154">
-        <v>-0.887075662612915</v>
+        <v>-0.6110196113586426</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3585,7 +3585,7 @@
         <v>-9</v>
       </c>
       <c r="D155">
-        <v>-2.072661638259888</v>
+        <v>-3.724093675613403</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3599,7 +3599,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D156">
-        <v>2.99173378944397</v>
+        <v>4.377360343933105</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3613,7 +3613,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D157">
-        <v>1.023955345153809</v>
+        <v>-5.922685146331787</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3627,7 +3627,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D158">
-        <v>-17.96786499023438</v>
+        <v>-19.10683822631836</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3641,7 +3641,7 @@
         <v>-30.79999923706055</v>
       </c>
       <c r="D159">
-        <v>-13.95610809326172</v>
+        <v>-17.52609443664551</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3655,7 +3655,7 @@
         <v>-11.5</v>
       </c>
       <c r="D160">
-        <v>-3.545909643173218</v>
+        <v>-3.474591732025146</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3669,7 +3669,7 @@
         <v>-21.60000038146973</v>
       </c>
       <c r="D161">
-        <v>-17.3845272064209</v>
+        <v>-19.0501651763916</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3683,7 +3683,7 @@
         <v>-14.60000038146973</v>
       </c>
       <c r="D162">
-        <v>-13.17081451416016</v>
+        <v>-10.02771663665771</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3697,7 +3697,7 @@
         <v>-2.5</v>
       </c>
       <c r="D163">
-        <v>-2.803751707077026</v>
+        <v>-3.987405300140381</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3711,7 +3711,7 @@
         <v>2</v>
       </c>
       <c r="D164">
-        <v>3.963774442672729</v>
+        <v>2.681409120559692</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3725,7 +3725,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D165">
-        <v>-1.309064388275146</v>
+        <v>-1.396069765090942</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3739,7 +3739,7 @@
         <v>-12.39999961853027</v>
       </c>
       <c r="D166">
-        <v>-17.98396492004395</v>
+        <v>-19.08149337768555</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3753,7 +3753,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D167">
-        <v>-0.0159890353679657</v>
+        <v>0.09768804907798767</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3767,7 +3767,7 @@
         <v>-2</v>
       </c>
       <c r="D168">
-        <v>0.884666919708252</v>
+        <v>1.612650036811829</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3781,7 +3781,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D169">
-        <v>-6.7578125</v>
+        <v>-6.562307357788086</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3795,7 +3795,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D170">
-        <v>0.9012812376022339</v>
+        <v>1.383090257644653</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3809,7 +3809,7 @@
         <v>-5</v>
       </c>
       <c r="D171">
-        <v>2.233896017074585</v>
+        <v>1.088607549667358</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3823,7 +3823,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D172">
-        <v>-0.472447007894516</v>
+        <v>-0.4113381505012512</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3837,7 +3837,7 @@
         <v>-14.10000038146973</v>
       </c>
       <c r="D173">
-        <v>-10.2446231842041</v>
+        <v>-10.6828145980835</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3851,7 +3851,7 @@
         <v>-6.599999904632568</v>
       </c>
       <c r="D174">
-        <v>-9.759696960449219</v>
+        <v>-10.03160667419434</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3865,7 +3865,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D175">
-        <v>9.197429656982422</v>
+        <v>10.08499336242676</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3879,7 +3879,7 @@
         <v>-18.5</v>
       </c>
       <c r="D176">
-        <v>-16.86162757873535</v>
+        <v>-17.74679565429688</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3893,7 +3893,7 @@
         <v>-16.20000076293945</v>
       </c>
       <c r="D177">
-        <v>-9.803131103515625</v>
+        <v>-10.52143383026123</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3907,7 +3907,7 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>-2.211865186691284</v>
+        <v>-1.49785590171814</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3921,7 +3921,7 @@
         <v>25.29999923706055</v>
       </c>
       <c r="D179">
-        <v>13.8914852142334</v>
+        <v>14.70062255859375</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3935,7 +3935,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D180">
-        <v>-10.83090496063232</v>
+        <v>-9.192042350769043</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3949,7 +3949,7 @@
         <v>-7.300000190734863</v>
       </c>
       <c r="D181">
-        <v>-6.867533683776855</v>
+        <v>-6.335738658905029</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3963,7 +3963,7 @@
         <v>-7.300000190734863</v>
       </c>
       <c r="D182">
-        <v>-8.71282958984375</v>
+        <v>-6.190985679626465</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3977,7 +3977,7 @@
         <v>-24</v>
       </c>
       <c r="D183">
-        <v>-5.383449554443359</v>
+        <v>-5.425632953643799</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3991,7 +3991,7 @@
         <v>-9</v>
       </c>
       <c r="D184">
-        <v>-3.161169767379761</v>
+        <v>-5.221785545349121</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4005,7 +4005,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D185">
-        <v>-0.2326392382383347</v>
+        <v>0.2985884845256805</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4019,7 +4019,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D186">
-        <v>5.430582046508789</v>
+        <v>5.408329486846924</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4033,7 +4033,7 @@
         <v>-5</v>
       </c>
       <c r="D187">
-        <v>-4.587578296661377</v>
+        <v>-5.773067474365234</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4047,7 +4047,7 @@
         <v>-10.69999980926514</v>
       </c>
       <c r="D188">
-        <v>-8.478403091430664</v>
+        <v>-12.58659648895264</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4061,7 +4061,7 @@
         <v>-23.79999923706055</v>
       </c>
       <c r="D189">
-        <v>-13.43574523925781</v>
+        <v>-12.01046752929688</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4075,7 +4075,7 @@
         <v>-2</v>
       </c>
       <c r="D190">
-        <v>0.758208155632019</v>
+        <v>0.8944243192672729</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4089,7 +4089,7 @@
         <v>0.5</v>
       </c>
       <c r="D191">
-        <v>-2.74117112159729</v>
+        <v>-3.299121856689453</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4103,7 +4103,7 @@
         <v>-38.79999923706055</v>
       </c>
       <c r="D192">
-        <v>-11.49480533599854</v>
+        <v>-17.26497650146484</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4117,7 +4117,7 @@
         <v>-17.70000076293945</v>
       </c>
       <c r="D193">
-        <v>-14.81300258636475</v>
+        <v>-16.43315124511719</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4131,7 +4131,7 @@
         <v>13.30000019073486</v>
       </c>
       <c r="D194">
-        <v>5.676247596740723</v>
+        <v>6.030357837677002</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4145,7 +4145,7 @@
         <v>-18.39999961853027</v>
       </c>
       <c r="D195">
-        <v>-16.28312873840332</v>
+        <v>-18.48037719726562</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4159,7 +4159,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D196">
-        <v>3.976249933242798</v>
+        <v>4.753439426422119</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4173,7 +4173,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D197">
-        <v>1.17638635635376</v>
+        <v>1.600834488868713</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4187,7 +4187,7 @@
         <v>-2</v>
       </c>
       <c r="D198">
-        <v>-0.70172119140625</v>
+        <v>-1.227260589599609</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4201,7 +4201,7 @@
         <v>-13.5</v>
       </c>
       <c r="D199">
-        <v>-6.701871871948242</v>
+        <v>-7.393548965454102</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4215,7 +4215,7 @@
         <v>-16.39999961853027</v>
       </c>
       <c r="D200">
-        <v>-11.28936767578125</v>
+        <v>-9.97592830657959</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4229,7 +4229,7 @@
         <v>-11.10000038146973</v>
       </c>
       <c r="D201">
-        <v>-8.682440757751465</v>
+        <v>-10.79891681671143</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4243,7 +4243,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D202">
-        <v>-3.305484771728516</v>
+        <v>-3.222214460372925</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4257,7 +4257,7 @@
         <v>4</v>
       </c>
       <c r="D203">
-        <v>1.483392596244812</v>
+        <v>1.235704779624939</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4271,7 +4271,7 @@
         <v>-14.5</v>
       </c>
       <c r="D204">
-        <v>-7.301214218139648</v>
+        <v>-8.762871742248535</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4285,7 +4285,7 @@
         <v>-3.5</v>
       </c>
       <c r="D205">
-        <v>-2.909166812896729</v>
+        <v>-3.985897302627563</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4299,7 +4299,7 @@
         <v>-4.5</v>
       </c>
       <c r="D206">
-        <v>-4.287325382232666</v>
+        <v>-6.398917198181152</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4313,7 +4313,7 @@
         <v>-5</v>
       </c>
       <c r="D207">
-        <v>-9.324159622192383</v>
+        <v>-8.726212501525879</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4327,7 +4327,7 @@
         <v>16.29999923706055</v>
       </c>
       <c r="D208">
-        <v>11.57653331756592</v>
+        <v>13.09270191192627</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4341,7 +4341,7 @@
         <v>-19.79999923706055</v>
       </c>
       <c r="D209">
-        <v>-17.50134468078613</v>
+        <v>-19.08732604980469</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4355,7 +4355,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D210">
-        <v>-1.150497317314148</v>
+        <v>-1.376154541969299</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4369,7 +4369,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D211">
-        <v>-0.03904372453689575</v>
+        <v>0.8344833850860596</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4383,7 +4383,7 @@
         <v>23.39999961853027</v>
       </c>
       <c r="D212">
-        <v>-9.468462944030762</v>
+        <v>-8.596516609191895</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4397,7 +4397,7 @@
         <v>-4.5</v>
       </c>
       <c r="D213">
-        <v>-2.061414003372192</v>
+        <v>-2.602392196655273</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4411,7 +4411,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D214">
-        <v>-0.1741796731948853</v>
+        <v>-0.2447091042995453</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4425,7 +4425,7 @@
         <v>-8.699999809265137</v>
       </c>
       <c r="D215">
-        <v>-6.264684200286865</v>
+        <v>-6.10899019241333</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4439,7 +4439,7 @@
         <v>-7.800000190734863</v>
       </c>
       <c r="D216">
-        <v>-6.921531200408936</v>
+        <v>-5.784048557281494</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4453,7 +4453,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D217">
-        <v>2.528482675552368</v>
+        <v>1.779945492744446</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4467,7 +4467,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D218">
-        <v>1.215255737304688</v>
+        <v>-0.6339946389198303</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4481,7 +4481,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D219">
-        <v>3.000628232955933</v>
+        <v>2.452124118804932</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4495,7 +4495,7 @@
         <v>-9</v>
       </c>
       <c r="D220">
-        <v>-9.142308235168457</v>
+        <v>-9.120255470275879</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4509,7 +4509,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D221">
-        <v>-0.456499308347702</v>
+        <v>0.412177175283432</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4523,7 +4523,7 @@
         <v>-34.70000076293945</v>
       </c>
       <c r="D222">
-        <v>-10.0513858795166</v>
+        <v>-9.560298919677734</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4537,7 +4537,7 @@
         <v>-11.19999980926514</v>
       </c>
       <c r="D223">
-        <v>-4.334089279174805</v>
+        <v>-4.962653636932373</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4551,7 +4551,7 @@
         <v>-17.10000038146973</v>
       </c>
       <c r="D224">
-        <v>-11.74113178253174</v>
+        <v>-11.93570232391357</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4565,7 +4565,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D225">
-        <v>3.254184722900391</v>
+        <v>2.571638345718384</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4579,7 +4579,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D226">
-        <v>4.46489953994751</v>
+        <v>2.932498216629028</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4593,7 +4593,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D227">
-        <v>4.162771224975586</v>
+        <v>5.183081150054932</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4607,7 +4607,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D228">
-        <v>1.161211609840393</v>
+        <v>1.134870052337646</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4621,7 +4621,7 @@
         <v>-8</v>
       </c>
       <c r="D229">
-        <v>-1.809691667556763</v>
+        <v>-3.446751832962036</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4635,7 +4635,7 @@
         <v>-1.5</v>
       </c>
       <c r="D230">
-        <v>0.01808992028236389</v>
+        <v>0.0825975239276886</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4649,7 +4649,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D231">
-        <v>0.5791666507720947</v>
+        <v>0.307356208562851</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4663,7 +4663,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D232">
-        <v>0.4898726642131805</v>
+        <v>0.9673886299133301</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4677,7 +4677,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D233">
-        <v>2.039618730545044</v>
+        <v>1.35103702545166</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4691,7 +4691,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D234">
-        <v>4.303983688354492</v>
+        <v>4.198907375335693</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4705,7 +4705,7 @@
         <v>22.20000076293945</v>
       </c>
       <c r="D235">
-        <v>15.93661117553711</v>
+        <v>16.70597267150879</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4719,7 +4719,7 @@
         <v>-6.400000095367432</v>
       </c>
       <c r="D236">
-        <v>-7.446704864501953</v>
+        <v>-9.397759437561035</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4733,7 +4733,7 @@
         <v>-14.39999961853027</v>
       </c>
       <c r="D237">
-        <v>-4.927756309509277</v>
+        <v>-6.757139205932617</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4747,7 +4747,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D238">
-        <v>-0.3442379236221313</v>
+        <v>0.7942219972610474</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4761,7 +4761,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D239">
-        <v>-0.1733504384756088</v>
+        <v>0.6415536403656006</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4775,7 +4775,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D240">
-        <v>-0.5905029773712158</v>
+        <v>-0.5936079025268555</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4789,7 +4789,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D241">
-        <v>-2.469928026199341</v>
+        <v>-3.031411409378052</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4803,7 +4803,7 @@
         <v>-11.89999961853027</v>
       </c>
       <c r="D242">
-        <v>1.06812858581543</v>
+        <v>0.9772332906723022</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4817,7 +4817,7 @@
         <v>-11.19999980926514</v>
       </c>
       <c r="D243">
-        <v>-6.755663871765137</v>
+        <v>-7.493468761444092</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4831,7 +4831,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D244">
-        <v>1.64631724357605</v>
+        <v>1.993125081062317</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4845,7 +4845,7 @@
         <v>-7.800000190734863</v>
       </c>
       <c r="D245">
-        <v>-5.736018180847168</v>
+        <v>-4.457068920135498</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4859,7 +4859,7 @@
         <v>-7.099999904632568</v>
       </c>
       <c r="D246">
-        <v>-6.833825588226318</v>
+        <v>-6.795585155487061</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4873,7 +4873,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D247">
-        <v>-0.6733341217041016</v>
+        <v>-1.113482356071472</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4887,7 +4887,7 @@
         <v>-8.800000190734863</v>
       </c>
       <c r="D248">
-        <v>-5.436502933502197</v>
+        <v>-4.335705757141113</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4901,7 +4901,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D249">
-        <v>-0.7754642963409424</v>
+        <v>-2.316545724868774</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4915,7 +4915,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D250">
-        <v>-1.975670456886292</v>
+        <v>-3.965242147445679</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4929,7 +4929,7 @@
         <v>-7.5</v>
       </c>
       <c r="D251">
-        <v>-2.996279001235962</v>
+        <v>-6.01232385635376</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4943,7 +4943,7 @@
         <v>-20.89999961853027</v>
       </c>
       <c r="D252">
-        <v>-8.811424255371094</v>
+        <v>-6.867873191833496</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4957,7 +4957,7 @@
         <v>-15.60000038146973</v>
       </c>
       <c r="D253">
-        <v>-11.54204368591309</v>
+        <v>-14.6249303817749</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4971,7 +4971,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D254">
-        <v>-6.054605484008789</v>
+        <v>-7.180126190185547</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4985,7 +4985,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D255">
-        <v>1.566033720970154</v>
+        <v>1.35602879524231</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4999,7 +4999,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D256">
-        <v>1.235361456871033</v>
+        <v>2.820887804031372</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -5013,7 +5013,7 @@
         <v>-8.300000190734863</v>
       </c>
       <c r="D257">
-        <v>-6.654305934906006</v>
+        <v>-7.171422481536865</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -5027,7 +5027,7 @@
         <v>-12.39999961853027</v>
       </c>
       <c r="D258">
-        <v>-9.091470718383789</v>
+        <v>-8.37879753112793</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -5041,7 +5041,7 @@
         <v>-9.800000190734863</v>
       </c>
       <c r="D259">
-        <v>-8.44127082824707</v>
+        <v>-8.348034858703613</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -5055,7 +5055,7 @@
         <v>-10.5</v>
       </c>
       <c r="D260">
-        <v>-3.569051265716553</v>
+        <v>-3.87737250328064</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -5069,7 +5069,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D261">
-        <v>2.551130056381226</v>
+        <v>4.200090885162354</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -5083,7 +5083,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D262">
-        <v>-4.715590476989746</v>
+        <v>-5.416803359985352</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -5097,7 +5097,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D263">
-        <v>0.4094030559062958</v>
+        <v>0.304431289434433</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -5111,7 +5111,7 @@
         <v>-5</v>
       </c>
       <c r="D264">
-        <v>-2.020168542861938</v>
+        <v>-1.547840118408203</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -5125,7 +5125,7 @@
         <v>15.5</v>
       </c>
       <c r="D265">
-        <v>7.867208480834961</v>
+        <v>9.120364189147949</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -5139,7 +5139,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D266">
-        <v>-0.5772517919540405</v>
+        <v>-0.4683391451835632</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -5153,7 +5153,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D267">
-        <v>-1.065404415130615</v>
+        <v>-0.01437109708786011</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -5167,7 +5167,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D268">
-        <v>-0.2176554650068283</v>
+        <v>0.3592034876346588</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -5181,7 +5181,7 @@
         <v>18.89999961853027</v>
       </c>
       <c r="D269">
-        <v>7.091048240661621</v>
+        <v>6.578702449798584</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -5195,7 +5195,7 @@
         <v>-8.600000381469727</v>
       </c>
       <c r="D270">
-        <v>-4.579727649688721</v>
+        <v>-5.926619052886963</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -5209,7 +5209,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D271">
-        <v>-1.729122638702393</v>
+        <v>-2.414835691452026</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -5223,7 +5223,7 @@
         <v>-18.20000076293945</v>
       </c>
       <c r="D272">
-        <v>-16.9505672454834</v>
+        <v>-18.95906448364258</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -5237,7 +5237,7 @@
         <v>-20.79999923706055</v>
       </c>
       <c r="D273">
-        <v>-15.95879650115967</v>
+        <v>-9.844487190246582</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -5251,7 +5251,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D274">
-        <v>1.592287063598633</v>
+        <v>1.867809891700745</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5265,7 +5265,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D275">
-        <v>-3.146248340606689</v>
+        <v>-4.757256984710693</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5279,7 +5279,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D276">
-        <v>1.808311939239502</v>
+        <v>2.564926147460938</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5293,7 +5293,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D277">
-        <v>-1.78719162940979</v>
+        <v>-0.6826716661453247</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5307,7 +5307,7 @@
         <v>-15</v>
       </c>
       <c r="D278">
-        <v>-12.94160938262939</v>
+        <v>-9.152029991149902</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5321,7 +5321,7 @@
         <v>-6.199999809265137</v>
       </c>
       <c r="D279">
-        <v>-7.347534656524658</v>
+        <v>-6.696177959442139</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5335,7 +5335,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D280">
-        <v>1.485875606536865</v>
+        <v>1.226790547370911</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5349,7 +5349,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D281">
-        <v>-4.981753349304199</v>
+        <v>-3.967755079269409</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5363,7 +5363,7 @@
         <v>15.69999980926514</v>
       </c>
       <c r="D282">
-        <v>1.534816980361938</v>
+        <v>1.852235198020935</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5377,7 +5377,7 @@
         <v>-3</v>
       </c>
       <c r="D283">
-        <v>-2.755475044250488</v>
+        <v>-2.11273980140686</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5391,7 +5391,7 @@
         <v>0</v>
       </c>
       <c r="D284">
-        <v>1.76453685760498</v>
+        <v>1.312245726585388</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5405,7 +5405,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D285">
-        <v>0.2711051404476166</v>
+        <v>1.407060503959656</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5419,7 +5419,7 @@
         <v>-10.89999961853027</v>
       </c>
       <c r="D286">
-        <v>-8.644332885742188</v>
+        <v>-8.825461387634277</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5433,7 +5433,7 @@
         <v>2</v>
       </c>
       <c r="D287">
-        <v>0.7329258918762207</v>
+        <v>0.9340444803237915</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5447,7 +5447,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D288">
-        <v>1.946096181869507</v>
+        <v>1.19504189491272</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5461,7 +5461,7 @@
         <v>8</v>
       </c>
       <c r="D289">
-        <v>3.218119382858276</v>
+        <v>3.010483026504517</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5475,7 +5475,7 @@
         <v>-11.30000019073486</v>
       </c>
       <c r="D290">
-        <v>-9.192966461181641</v>
+        <v>-10.59685325622559</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5489,7 +5489,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D291">
-        <v>0.9681048393249512</v>
+        <v>1.651785016059875</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5503,7 +5503,7 @@
         <v>-9.899999618530273</v>
       </c>
       <c r="D292">
-        <v>-7.014340400695801</v>
+        <v>-8.821375846862793</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5517,7 +5517,7 @@
         <v>-7.5</v>
       </c>
       <c r="D293">
-        <v>-5.198814868927002</v>
+        <v>-2.996609449386597</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5531,7 +5531,7 @@
         <v>-4.900000095367432</v>
       </c>
       <c r="D294">
-        <v>-8.965127944946289</v>
+        <v>-8.222519874572754</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5545,7 +5545,7 @@
         <v>-4.900000095367432</v>
       </c>
       <c r="D295">
-        <v>-3.149425268173218</v>
+        <v>-2.328201293945312</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5559,7 +5559,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D296">
-        <v>0.3828830420970917</v>
+        <v>-0.630308985710144</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5573,7 +5573,7 @@
         <v>-7.199999809265137</v>
       </c>
       <c r="D297">
-        <v>-4.050220012664795</v>
+        <v>-5.741870403289795</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5587,7 +5587,7 @@
         <v>-15.60000038146973</v>
       </c>
       <c r="D298">
-        <v>-12.77559471130371</v>
+        <v>-12.80588626861572</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5601,7 +5601,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D299">
-        <v>-4.419490814208984</v>
+        <v>-5.633109569549561</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5615,7 +5615,7 @@
         <v>-11.5</v>
       </c>
       <c r="D300">
-        <v>-6.182169914245605</v>
+        <v>-4.394209384918213</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5629,7 +5629,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D301">
-        <v>-1.276522755622864</v>
+        <v>-0.9783424139022827</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5643,7 +5643,7 @@
         <v>-12.60000038146973</v>
       </c>
       <c r="D302">
-        <v>-5.906389713287354</v>
+        <v>-8.801168441772461</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5657,7 +5657,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D303">
-        <v>-0.3301607370376587</v>
+        <v>-0.09168294072151184</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5671,7 +5671,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D304">
-        <v>1.301354885101318</v>
+        <v>1.011563658714294</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5685,7 +5685,7 @@
         <v>-11.69999980926514</v>
       </c>
       <c r="D305">
-        <v>-8.949343681335449</v>
+        <v>-9.50284481048584</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5699,7 +5699,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D306">
-        <v>-2.203619956970215</v>
+        <v>-3.248878955841064</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5713,7 +5713,7 @@
         <v>5.5</v>
       </c>
       <c r="D307">
-        <v>1.565471172332764</v>
+        <v>-0.3729316592216492</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5727,7 +5727,7 @@
         <v>-5.5</v>
       </c>
       <c r="D308">
-        <v>-4.510755062103271</v>
+        <v>-3.678890466690063</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5741,7 +5741,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D309">
-        <v>1.467705011367798</v>
+        <v>2.410503149032593</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5755,7 +5755,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D310">
-        <v>-4.694753170013428</v>
+        <v>-5.754843235015869</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5769,7 +5769,7 @@
         <v>-4.199999809265137</v>
       </c>
       <c r="D311">
-        <v>-5.815307140350342</v>
+        <v>-6.944197177886963</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5783,7 +5783,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D312">
-        <v>-1.815152168273926</v>
+        <v>-3.479311227798462</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5797,7 +5797,7 @@
         <v>11.5</v>
       </c>
       <c r="D313">
-        <v>4.086867809295654</v>
+        <v>3.211469888687134</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5811,7 +5811,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D314">
-        <v>1.690791845321655</v>
+        <v>2.949445486068726</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -5825,7 +5825,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D315">
-        <v>1.27497124671936</v>
+        <v>1.860746026039124</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -5839,7 +5839,7 @@
         <v>-4.099999904632568</v>
       </c>
       <c r="D316">
-        <v>-5.176302909851074</v>
+        <v>-6.305154800415039</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -5853,7 +5853,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D317">
-        <v>0.2733819782733917</v>
+        <v>0.7116776704788208</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -5867,7 +5867,7 @@
         <v>-7.800000190734863</v>
       </c>
       <c r="D318">
-        <v>-8.329989433288574</v>
+        <v>-7.137701988220215</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -5881,7 +5881,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D319">
-        <v>-0.4409875869750977</v>
+        <v>-0.4016121625900269</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -5895,7 +5895,7 @@
         <v>13.30000019073486</v>
       </c>
       <c r="D320">
-        <v>9.084867477416992</v>
+        <v>8.510392189025879</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -5909,7 +5909,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D321">
-        <v>-3.820138216018677</v>
+        <v>-2.966436147689819</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -5923,7 +5923,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D322">
-        <v>7.059685707092285</v>
+        <v>5.321214199066162</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -5937,7 +5937,7 @@
         <v>-20.39999961853027</v>
       </c>
       <c r="D323">
-        <v>-17.6351146697998</v>
+        <v>-18.42071914672852</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -5951,7 +5951,7 @@
         <v>12.69999980926514</v>
       </c>
       <c r="D324">
-        <v>8.264572143554688</v>
+        <v>7.607367992401123</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -5965,7 +5965,7 @@
         <v>-22.39999961853027</v>
       </c>
       <c r="D325">
-        <v>-16.04204177856445</v>
+        <v>-16.52279663085938</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -5979,7 +5979,7 @@
         <v>-7.800000190734863</v>
       </c>
       <c r="D326">
-        <v>2.826156377792358</v>
+        <v>1.541487574577332</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -5993,7 +5993,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D327">
-        <v>-7.10910701751709</v>
+        <v>-9.533644676208496</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -6007,7 +6007,7 @@
         <v>17.29999923706055</v>
       </c>
       <c r="D328">
-        <v>3.747614622116089</v>
+        <v>4.1531662940979</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -6021,7 +6021,7 @@
         <v>21.5</v>
       </c>
       <c r="D329">
-        <v>10.05550193786621</v>
+        <v>10.04023361206055</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -6035,7 +6035,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D330">
-        <v>0.06668630242347717</v>
+        <v>0.2821561992168427</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -6049,7 +6049,7 @@
         <v>1</v>
       </c>
       <c r="D331">
-        <v>3.988765001296997</v>
+        <v>3.23989462852478</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -6063,7 +6063,7 @@
         <v>-16.60000038146973</v>
       </c>
       <c r="D332">
-        <v>-15.87709808349609</v>
+        <v>-17.06977081298828</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -6077,7 +6077,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D333">
-        <v>-9.977607727050781</v>
+        <v>-10.45706176757812</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -6091,7 +6091,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D334">
-        <v>-1.940038084983826</v>
+        <v>-3.483373880386353</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -6105,7 +6105,7 @@
         <v>-14.39999961853027</v>
       </c>
       <c r="D335">
-        <v>-4.889997482299805</v>
+        <v>-6.078941822052002</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -6119,7 +6119,7 @@
         <v>-12.5</v>
       </c>
       <c r="D336">
-        <v>-8.514856338500977</v>
+        <v>-8.403257369995117</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -6133,7 +6133,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D337">
-        <v>-7.182406425476074</v>
+        <v>-6.721549510955811</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -6147,7 +6147,7 @@
         <v>-10.60000038146973</v>
       </c>
       <c r="D338">
-        <v>-3.448279857635498</v>
+        <v>-3.768159627914429</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -6161,7 +6161,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D339">
-        <v>-2.418205738067627</v>
+        <v>-1.007583856582642</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -6175,7 +6175,7 @@
         <v>-1</v>
       </c>
       <c r="D340">
-        <v>-1.295331358909607</v>
+        <v>-0.8864314556121826</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -6189,7 +6189,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D341">
-        <v>-0.7892241477966309</v>
+        <v>-0.6722756624221802</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -6203,7 +6203,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D342">
-        <v>-1.863465785980225</v>
+        <v>-1.526733994483948</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -6217,7 +6217,7 @@
         <v>-7.400000095367432</v>
       </c>
       <c r="D343">
-        <v>-3.936176061630249</v>
+        <v>-4.938346385955811</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -6231,7 +6231,7 @@
         <v>-14.10000038146973</v>
       </c>
       <c r="D344">
-        <v>-8.76417350769043</v>
+        <v>-8.256821632385254</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -6245,7 +6245,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D345">
-        <v>6.927499294281006</v>
+        <v>2.785731554031372</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -6259,7 +6259,7 @@
         <v>7</v>
       </c>
       <c r="D346">
-        <v>0.1533732116222382</v>
+        <v>0.6939263343811035</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6273,7 +6273,7 @@
         <v>-11.89999961853027</v>
       </c>
       <c r="D347">
-        <v>-11.29707145690918</v>
+        <v>-8.860079765319824</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6287,7 +6287,7 @@
         <v>13.10000038146973</v>
       </c>
       <c r="D348">
-        <v>10.55051612854004</v>
+        <v>11.727952003479</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6301,7 +6301,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D349">
-        <v>0.8322852849960327</v>
+        <v>1.060507416725159</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6315,7 +6315,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D350">
-        <v>-2.916367053985596</v>
+        <v>-2.872276306152344</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6329,7 +6329,7 @@
         <v>-4</v>
       </c>
       <c r="D351">
-        <v>-1.870416760444641</v>
+        <v>-1.97700834274292</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6343,7 +6343,7 @@
         <v>0</v>
       </c>
       <c r="D352">
-        <v>-13.4309720993042</v>
+        <v>-14.06381607055664</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6357,7 +6357,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D353">
-        <v>-0.1369311809539795</v>
+        <v>0.3222724497318268</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6371,7 +6371,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D354">
-        <v>3.701711893081665</v>
+        <v>2.171720266342163</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6385,7 +6385,7 @@
         <v>-14.19999980926514</v>
       </c>
       <c r="D355">
-        <v>-6.316356658935547</v>
+        <v>-5.977747917175293</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6399,7 +6399,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D356">
-        <v>5.283616542816162</v>
+        <v>5.453759670257568</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6413,7 +6413,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D357">
-        <v>-0.6739485263824463</v>
+        <v>-0.3460055291652679</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6427,7 +6427,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D358">
-        <v>-2.002224683761597</v>
+        <v>-3.195163011550903</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6441,7 +6441,7 @@
         <v>-11.30000019073486</v>
       </c>
       <c r="D359">
-        <v>-9.174997329711914</v>
+        <v>-8.380697250366211</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6455,7 +6455,7 @@
         <v>0.5</v>
       </c>
       <c r="D360">
-        <v>1.166529059410095</v>
+        <v>0.6960445642471313</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6469,7 +6469,7 @@
         <v>-5.800000190734863</v>
       </c>
       <c r="D361">
-        <v>-10.08001899719238</v>
+        <v>-7.961856365203857</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6483,7 +6483,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D362">
-        <v>-5.425804615020752</v>
+        <v>-4.952038288116455</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6497,7 +6497,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D363">
-        <v>0.3622309863567352</v>
+        <v>1.223283410072327</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6511,7 +6511,7 @@
         <v>-6.5</v>
       </c>
       <c r="D364">
-        <v>-2.159492015838623</v>
+        <v>-2.010044813156128</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6525,7 +6525,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D365">
-        <v>3.190652132034302</v>
+        <v>2.791854381561279</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6539,7 +6539,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D366">
-        <v>-3.009718656539917</v>
+        <v>-3.085046052932739</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6553,7 +6553,7 @@
         <v>-11.39999961853027</v>
       </c>
       <c r="D367">
-        <v>-10.33408737182617</v>
+        <v>-10.71592807769775</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6567,7 +6567,7 @@
         <v>-40.90000152587891</v>
       </c>
       <c r="D368">
-        <v>-22.38921928405762</v>
+        <v>-27.41728973388672</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6581,7 +6581,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D369">
-        <v>-1.894733786582947</v>
+        <v>-3.585564613342285</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -6595,7 +6595,7 @@
         <v>-17.5</v>
       </c>
       <c r="D370">
-        <v>-12.18140506744385</v>
+        <v>-13.32136058807373</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -6609,7 +6609,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D371">
-        <v>-3.466534376144409</v>
+        <v>-4.356528282165527</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -6623,7 +6623,7 @@
         <v>-6.900000095367432</v>
       </c>
       <c r="D372">
-        <v>-5.426885604858398</v>
+        <v>-4.279426097869873</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -6637,7 +6637,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D373">
-        <v>-0.7271478176116943</v>
+        <v>0.7199890613555908</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -6651,7 +6651,7 @@
         <v>-6.900000095367432</v>
       </c>
       <c r="D374">
-        <v>-7.106407165527344</v>
+        <v>-5.961376667022705</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -6665,7 +6665,7 @@
         <v>-20.39999961853027</v>
       </c>
       <c r="D375">
-        <v>-2.462718963623047</v>
+        <v>1.312978625297546</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -6679,7 +6679,7 @@
         <v>0.5</v>
       </c>
       <c r="D376">
-        <v>3.221141815185547</v>
+        <v>2.540655612945557</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -6693,7 +6693,7 @@
         <v>-5.599999904632568</v>
       </c>
       <c r="D377">
-        <v>-4.080095291137695</v>
+        <v>-4.730220317840576</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -6707,7 +6707,7 @@
         <v>-7.099999904632568</v>
       </c>
       <c r="D378">
-        <v>-8.372834205627441</v>
+        <v>-9.452946662902832</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -6721,7 +6721,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D379">
-        <v>-0.07624027132987976</v>
+        <v>-2.787667989730835</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -6735,7 +6735,7 @@
         <v>-7</v>
       </c>
       <c r="D380">
-        <v>-9.226448059082031</v>
+        <v>-9.774537086486816</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -6749,7 +6749,7 @@
         <v>-14.19999980926514</v>
       </c>
       <c r="D381">
-        <v>-7.797011375427246</v>
+        <v>-6.657979488372803</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -6763,7 +6763,7 @@
         <v>1.5</v>
       </c>
       <c r="D382">
-        <v>-0.100632518529892</v>
+        <v>-0.2095450758934021</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -6777,7 +6777,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D383">
-        <v>-0.3909928500652313</v>
+        <v>-0.538878858089447</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -6791,7 +6791,7 @@
         <v>-2</v>
       </c>
       <c r="D384">
-        <v>-2.771783590316772</v>
+        <v>-2.185020446777344</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -6805,7 +6805,7 @@
         <v>-8</v>
       </c>
       <c r="D385">
-        <v>0.08943861722946167</v>
+        <v>-1.668567299842834</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -6819,7 +6819,7 @@
         <v>-8.800000190734863</v>
       </c>
       <c r="D386">
-        <v>-0.4239018559455872</v>
+        <v>-3.101814270019531</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -6833,7 +6833,7 @@
         <v>-11.5</v>
       </c>
       <c r="D387">
-        <v>-9.355817794799805</v>
+        <v>-9.086310386657715</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -6847,7 +6847,7 @@
         <v>-8.5</v>
       </c>
       <c r="D388">
-        <v>-9.275520324707031</v>
+        <v>-9.169722557067871</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -6861,7 +6861,7 @@
         <v>2.5</v>
       </c>
       <c r="D389">
-        <v>2.205890893936157</v>
+        <v>2.050817966461182</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -6875,7 +6875,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D390">
-        <v>-1.038618326187134</v>
+        <v>-1.208688974380493</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -6889,7 +6889,7 @@
         <v>-9.800000190734863</v>
       </c>
       <c r="D391">
-        <v>-9.828649520874023</v>
+        <v>-9.99171257019043</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -6903,7 +6903,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D392">
-        <v>1.188626646995544</v>
+        <v>2.001377582550049</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -6917,7 +6917,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D393">
-        <v>0.4753187596797943</v>
+        <v>0.5741308927536011</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -6931,7 +6931,7 @@
         <v>-8.899999618530273</v>
       </c>
       <c r="D394">
-        <v>-2.897028684616089</v>
+        <v>-6.573007106781006</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -6945,7 +6945,7 @@
         <v>-38</v>
       </c>
       <c r="D395">
-        <v>-16.58989715576172</v>
+        <v>-20.22879028320312</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -6959,7 +6959,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D396">
-        <v>-3.745036840438843</v>
+        <v>-3.39923882484436</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -6973,7 +6973,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D397">
-        <v>-8.115140914916992</v>
+        <v>-9.938071250915527</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -6987,7 +6987,7 @@
         <v>-9.600000381469727</v>
       </c>
       <c r="D398">
-        <v>-5.921189308166504</v>
+        <v>-6.539779186248779</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -7001,7 +7001,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D399">
-        <v>-1.086757659912109</v>
+        <v>-0.5507782101631165</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -7015,7 +7015,7 @@
         <v>-10.10000038146973</v>
       </c>
       <c r="D400">
-        <v>-3.265499830245972</v>
+        <v>-4.333670139312744</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -7029,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="D401">
-        <v>0.2742563784122467</v>
+        <v>1.741880059242249</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -7043,7 +7043,7 @@
         <v>9.5</v>
       </c>
       <c r="D402">
-        <v>3.512284517288208</v>
+        <v>2.567229032516479</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -7057,7 +7057,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D403">
-        <v>3.661798715591431</v>
+        <v>4.492486953735352</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -7071,7 +7071,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D404">
-        <v>0.3734907805919647</v>
+        <v>-1.181501269340515</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -7085,7 +7085,7 @@
         <v>-19.39999961853027</v>
       </c>
       <c r="D405">
-        <v>-17.3227710723877</v>
+        <v>-18.91454124450684</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -7099,7 +7099,7 @@
         <v>-11.5</v>
       </c>
       <c r="D406">
-        <v>-8.043618202209473</v>
+        <v>-8.744444847106934</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -7113,7 +7113,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D407">
-        <v>1.829003572463989</v>
+        <v>1.581775784492493</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -7127,7 +7127,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D408">
-        <v>-1.821706056594849</v>
+        <v>-3.365448236465454</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -7141,7 +7141,7 @@
         <v>-5.699999809265137</v>
       </c>
       <c r="D409">
-        <v>-4.114043712615967</v>
+        <v>-5.332735061645508</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -7155,7 +7155,7 @@
         <v>-8.800000190734863</v>
       </c>
       <c r="D410">
-        <v>-8.609293937683105</v>
+        <v>-8.416180610656738</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -7169,7 +7169,7 @@
         <v>-10.80000019073486</v>
       </c>
       <c r="D411">
-        <v>-4.264720439910889</v>
+        <v>-5.511827945709229</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -7183,7 +7183,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D412">
-        <v>-3.890040397644043</v>
+        <v>-2.859914064407349</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -7197,7 +7197,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D413">
-        <v>2.664861917495728</v>
+        <v>2.05531644821167</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -7211,7 +7211,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D414">
-        <v>2.433370351791382</v>
+        <v>2.052138805389404</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -7225,7 +7225,7 @@
         <v>-4.199999809265137</v>
       </c>
       <c r="D415">
-        <v>-1.558037161827087</v>
+        <v>-2.091742992401123</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -7239,7 +7239,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D416">
-        <v>2.239700317382812</v>
+        <v>2.133013010025024</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -7253,7 +7253,7 @@
         <v>-14.39999961853027</v>
       </c>
       <c r="D417">
-        <v>-6.287059307098389</v>
+        <v>-7.528533458709717</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -7267,7 +7267,7 @@
         <v>-20.70000076293945</v>
       </c>
       <c r="D418">
-        <v>-17.58311080932617</v>
+        <v>-19.12772369384766</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -7281,7 +7281,7 @@
         <v>-12.30000019073486</v>
       </c>
       <c r="D419">
-        <v>0.2101522386074066</v>
+        <v>2.063341856002808</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -7295,7 +7295,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D420">
-        <v>0.8787996768951416</v>
+        <v>1.365458250045776</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -7309,7 +7309,7 @@
         <v>-9.600000381469727</v>
       </c>
       <c r="D421">
-        <v>-4.542685985565186</v>
+        <v>-5.460926532745361</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -7323,7 +7323,7 @@
         <v>-14.39999961853027</v>
       </c>
       <c r="D422">
-        <v>-5.983437061309814</v>
+        <v>-8.302504539489746</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -7337,7 +7337,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D423">
-        <v>-2.897458076477051</v>
+        <v>-4.299403190612793</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -7351,7 +7351,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D424">
-        <v>-0.2499720752239227</v>
+        <v>-0.1227583587169647</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -7365,7 +7365,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D425">
-        <v>0.3740451633930206</v>
+        <v>-0.09498950839042664</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -7379,7 +7379,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D426">
-        <v>0.1258566081523895</v>
+        <v>-0.08943852782249451</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -7393,7 +7393,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D427">
-        <v>-2.285445690155029</v>
+        <v>-1.108290553092957</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -7407,7 +7407,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D428">
-        <v>3.110694408416748</v>
+        <v>1.964466691017151</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -7421,7 +7421,7 @@
         <v>-3.5</v>
       </c>
       <c r="D429">
-        <v>-7.425434589385986</v>
+        <v>-2.863756895065308</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -7435,7 +7435,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D430">
-        <v>-2.82383918762207</v>
+        <v>-1.695442676544189</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -7449,7 +7449,7 @@
         <v>-29.60000038146973</v>
       </c>
       <c r="D431">
-        <v>-17.8341121673584</v>
+        <v>-19.82706451416016</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -7463,7 +7463,7 @@
         <v>-7.400000095367432</v>
       </c>
       <c r="D432">
-        <v>-3.085971593856812</v>
+        <v>-4.521848201751709</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -7477,7 +7477,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D433">
-        <v>1.691087007522583</v>
+        <v>1.234569549560547</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -7491,7 +7491,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D434">
-        <v>1.238763928413391</v>
+        <v>0.2961868345737457</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -7505,7 +7505,7 @@
         <v>-19.5</v>
       </c>
       <c r="D435">
-        <v>-15.1984748840332</v>
+        <v>-14.92302894592285</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -7519,7 +7519,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D436">
-        <v>0.2492310702800751</v>
+        <v>-0.6836885213851929</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -7533,7 +7533,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D437">
-        <v>0.175775021314621</v>
+        <v>-1.760367035865784</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -7547,7 +7547,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D438">
-        <v>-0.5528139472007751</v>
+        <v>-2.017814874649048</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -7561,7 +7561,7 @@
         <v>-18.5</v>
       </c>
       <c r="D439">
-        <v>1.729040384292603</v>
+        <v>1.925495266914368</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -7575,7 +7575,7 @@
         <v>-18</v>
       </c>
       <c r="D440">
-        <v>-14.66444778442383</v>
+        <v>-14.90331935882568</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -7589,7 +7589,7 @@
         <v>-8.5</v>
       </c>
       <c r="D441">
-        <v>-5.708358764648438</v>
+        <v>-6.881362438201904</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -7603,7 +7603,7 @@
         <v>-9</v>
       </c>
       <c r="D442">
-        <v>-9.513411521911621</v>
+        <v>-10.64358329772949</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -7617,7 +7617,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D443">
-        <v>0.4762832820415497</v>
+        <v>0.6876949071884155</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -7631,7 +7631,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D444">
-        <v>1.121567845344543</v>
+        <v>1.530233383178711</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -7645,7 +7645,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D445">
-        <v>1.469858765602112</v>
+        <v>-0.3094930946826935</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -7659,7 +7659,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D446">
-        <v>0.1387121975421906</v>
+        <v>0.447227269411087</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -7673,7 +7673,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D447">
-        <v>-1.121661424636841</v>
+        <v>-1.708084940910339</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -7687,7 +7687,7 @@
         <v>-14.69999980926514</v>
       </c>
       <c r="D448">
-        <v>-8.84257698059082</v>
+        <v>-8.763240814208984</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -7701,7 +7701,7 @@
         <v>-8.899999618530273</v>
       </c>
       <c r="D449">
-        <v>-6.206984043121338</v>
+        <v>-4.672382831573486</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -7715,7 +7715,7 @@
         <v>-16.60000038146973</v>
       </c>
       <c r="D450">
-        <v>-15.23147773742676</v>
+        <v>-14.3079309463501</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -7729,7 +7729,7 @@
         <v>-5.800000190734863</v>
       </c>
       <c r="D451">
-        <v>-6.754788398742676</v>
+        <v>-8.35261344909668</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -7743,7 +7743,7 @@
         <v>9</v>
       </c>
       <c r="D452">
-        <v>6.118327140808105</v>
+        <v>5.515902042388916</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -7757,7 +7757,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D453">
-        <v>-1.171013355255127</v>
+        <v>0.02991628646850586</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -7771,7 +7771,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D454">
-        <v>2.53637170791626</v>
+        <v>2.252584218978882</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -7785,7 +7785,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D455">
-        <v>4.792175769805908</v>
+        <v>4.750484943389893</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -7799,7 +7799,7 @@
         <v>-39.90000152587891</v>
       </c>
       <c r="D456">
-        <v>-26.70921897888184</v>
+        <v>-22.44524192810059</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -7813,7 +7813,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D457">
-        <v>-2.270500659942627</v>
+        <v>-1.811797022819519</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -7827,7 +7827,7 @@
         <v>-23.70000076293945</v>
       </c>
       <c r="D458">
-        <v>-20.23779106140137</v>
+        <v>-19.81656074523926</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -7841,7 +7841,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D459">
-        <v>0.3334961831569672</v>
+        <v>0.1941292583942413</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -7855,7 +7855,7 @@
         <v>-10.5</v>
       </c>
       <c r="D460">
-        <v>-0.9433104991912842</v>
+        <v>-0.5975163578987122</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -7869,7 +7869,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D461">
-        <v>5.009468078613281</v>
+        <v>5.967421531677246</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -7883,7 +7883,7 @@
         <v>-18.79999923706055</v>
       </c>
       <c r="D462">
-        <v>-13.75445938110352</v>
+        <v>-16.1274242401123</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -7897,7 +7897,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D463">
-        <v>2.059834718704224</v>
+        <v>1.844145894050598</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -7911,7 +7911,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D464">
-        <v>0.2027064263820648</v>
+        <v>0.2842706739902496</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -7925,7 +7925,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D465">
-        <v>0.935327410697937</v>
+        <v>0.9361357688903809</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -7939,7 +7939,7 @@
         <v>2</v>
       </c>
       <c r="D466">
-        <v>-1.353608012199402</v>
+        <v>-1.52792763710022</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -7953,7 +7953,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D467">
-        <v>0.07656577229499817</v>
+        <v>0.903632640838623</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -7967,7 +7967,7 @@
         <v>-11.60000038146973</v>
       </c>
       <c r="D468">
-        <v>-5.263609886169434</v>
+        <v>-2.598786115646362</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -7981,7 +7981,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D469">
-        <v>-0.3592472076416016</v>
+        <v>1.0343416929245</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -7995,7 +7995,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D470">
-        <v>-2.773167371749878</v>
+        <v>-3.900963068008423</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -8009,7 +8009,7 @@
         <v>-10.89999961853027</v>
       </c>
       <c r="D471">
-        <v>-9.145450592041016</v>
+        <v>-10.8200511932373</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -8023,7 +8023,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D472">
-        <v>-3.893107175827026</v>
+        <v>-3.574333906173706</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -8037,7 +8037,7 @@
         <v>-1.5</v>
       </c>
       <c r="D473">
-        <v>2.117922067642212</v>
+        <v>0.9004195928573608</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -8051,7 +8051,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D474">
-        <v>-0.2357536554336548</v>
+        <v>0.04242396354675293</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -8065,7 +8065,7 @@
         <v>-9.199999809265137</v>
       </c>
       <c r="D475">
-        <v>-8.675712585449219</v>
+        <v>-5.859396934509277</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -8079,7 +8079,7 @@
         <v>1</v>
       </c>
       <c r="D476">
-        <v>-0.3810651302337646</v>
+        <v>-0.3615610599517822</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -8093,7 +8093,7 @@
         <v>18.89999961853027</v>
       </c>
       <c r="D477">
-        <v>12.73737716674805</v>
+        <v>12.27857494354248</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -8107,7 +8107,7 @@
         <v>1.5</v>
       </c>
       <c r="D478">
-        <v>4.771854877471924</v>
+        <v>4.263740062713623</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -8121,7 +8121,7 @@
         <v>6.5</v>
       </c>
       <c r="D479">
-        <v>0.01424837112426758</v>
+        <v>0.9696788787841797</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -8135,7 +8135,7 @@
         <v>-2</v>
       </c>
       <c r="D480">
-        <v>0.07015517354011536</v>
+        <v>-1.973908066749573</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -8149,7 +8149,7 @@
         <v>0.5</v>
       </c>
       <c r="D481">
-        <v>0.3281416594982147</v>
+        <v>1.105351209640503</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -8163,7 +8163,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D482">
-        <v>-0.461480438709259</v>
+        <v>-1.140819072723389</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -8177,7 +8177,7 @@
         <v>-24.79999923706055</v>
       </c>
       <c r="D483">
-        <v>-14.32123470306396</v>
+        <v>-13.64544582366943</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -8191,7 +8191,7 @@
         <v>-5.5</v>
       </c>
       <c r="D484">
-        <v>-3.454231262207031</v>
+        <v>-3.148713350296021</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -8205,7 +8205,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D485">
-        <v>4.275002479553223</v>
+        <v>4.368760108947754</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -8219,7 +8219,7 @@
         <v>-5.5</v>
       </c>
       <c r="D486">
-        <v>-3.742681264877319</v>
+        <v>-3.050507307052612</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -8233,7 +8233,7 @@
         <v>-15</v>
       </c>
       <c r="D487">
-        <v>-11.05023765563965</v>
+        <v>-7.738462924957275</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -8247,7 +8247,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D488">
-        <v>-4.168047904968262</v>
+        <v>-5.815957069396973</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -8261,7 +8261,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D489">
-        <v>3.928656339645386</v>
+        <v>3.150367498397827</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -8275,7 +8275,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D490">
-        <v>0.4143120944499969</v>
+        <v>-0.005021482706069946</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -8289,7 +8289,7 @@
         <v>10.39999961853027</v>
       </c>
       <c r="D491">
-        <v>2.028080463409424</v>
+        <v>2.485408067703247</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -8303,7 +8303,7 @@
         <v>-7.099999904632568</v>
       </c>
       <c r="D492">
-        <v>1.077136516571045</v>
+        <v>-0.4577491581439972</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -8317,7 +8317,7 @@
         <v>-12.19999980926514</v>
       </c>
       <c r="D493">
-        <v>-5.108526229858398</v>
+        <v>-4.544730663299561</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -8331,7 +8331,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D494">
-        <v>1.421394944190979</v>
+        <v>-1.748187661170959</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -8345,7 +8345,7 @@
         <v>-16.39999961853027</v>
       </c>
       <c r="D495">
-        <v>-4.104153633117676</v>
+        <v>-3.532533168792725</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -8359,7 +8359,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D496">
-        <v>0.4348317682743073</v>
+        <v>1.198223948478699</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8373,7 +8373,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D497">
-        <v>5.737406730651855</v>
+        <v>5.129714012145996</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8387,7 +8387,7 @@
         <v>1.5</v>
       </c>
       <c r="D498">
-        <v>-2.651540994644165</v>
+        <v>-1.86670982837677</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -8401,7 +8401,7 @@
         <v>-12.60000038146973</v>
       </c>
       <c r="D499">
-        <v>-7.85455322265625</v>
+        <v>-8.991950035095215</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -8415,7 +8415,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D500">
-        <v>-2.995589971542358</v>
+        <v>-2.647947549819946</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8429,7 +8429,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D501">
-        <v>-0.1976141333580017</v>
+        <v>-0.02965214848518372</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -8443,7 +8443,7 @@
         <v>-7.400000095367432</v>
       </c>
       <c r="D502">
-        <v>-4.048932552337646</v>
+        <v>-5.410297870635986</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -8457,7 +8457,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D503">
-        <v>-7.26227855682373</v>
+        <v>-6.843978881835938</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -8471,7 +8471,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D504">
-        <v>2.081393003463745</v>
+        <v>1.080492377281189</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -8485,7 +8485,7 @@
         <v>-13.60000038146973</v>
       </c>
       <c r="D505">
-        <v>-10.89693355560303</v>
+        <v>-7.302996158599854</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -8499,7 +8499,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D506">
-        <v>10.6157922744751</v>
+        <v>11.65572166442871</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -8513,7 +8513,7 @@
         <v>-12.60000038146973</v>
       </c>
       <c r="D507">
-        <v>-5.269462585449219</v>
+        <v>-4.420229911804199</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -8527,7 +8527,7 @@
         <v>-10.60000038146973</v>
       </c>
       <c r="D508">
-        <v>-10.76027870178223</v>
+        <v>-8.53780460357666</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -8541,7 +8541,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D509">
-        <v>1.663383722305298</v>
+        <v>1.808781266212463</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -8555,7 +8555,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D510">
-        <v>3.103861331939697</v>
+        <v>2.762978792190552</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -8569,7 +8569,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D511">
-        <v>-1.342186212539673</v>
+        <v>-4.359096527099609</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -8583,7 +8583,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D512">
-        <v>-0.3399560451507568</v>
+        <v>-0.2819007039070129</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -8597,7 +8597,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D513">
-        <v>0.9469965696334839</v>
+        <v>-0.04853799939155579</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -8611,7 +8611,7 @@
         <v>-1</v>
       </c>
       <c r="D514">
-        <v>-3.776877164840698</v>
+        <v>-5.141171932220459</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -8625,7 +8625,7 @@
         <v>-6.199999809265137</v>
       </c>
       <c r="D515">
-        <v>-2.831255674362183</v>
+        <v>-3.412280559539795</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -8639,7 +8639,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D516">
-        <v>-5.263217926025391</v>
+        <v>-3.112921237945557</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -8653,7 +8653,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D517">
-        <v>-3.073623895645142</v>
+        <v>-3.838079214096069</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -8667,7 +8667,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D518">
-        <v>-0.05028021335601807</v>
+        <v>1.109552383422852</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -8681,7 +8681,7 @@
         <v>-7.900000095367432</v>
       </c>
       <c r="D519">
-        <v>-4.051998615264893</v>
+        <v>-5.049357891082764</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -8695,7 +8695,7 @@
         <v>-8</v>
       </c>
       <c r="D520">
-        <v>1.73788857460022</v>
+        <v>1.946501851081848</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -8709,7 +8709,7 @@
         <v>-5.599999904632568</v>
       </c>
       <c r="D521">
-        <v>1.788118362426758</v>
+        <v>2.184720277786255</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -8723,7 +8723,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D522">
-        <v>-6.783674240112305</v>
+        <v>-4.070504665374756</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -8737,7 +8737,7 @@
         <v>-6.599999904632568</v>
       </c>
       <c r="D523">
-        <v>-8.137908935546875</v>
+        <v>-6.985920429229736</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -8751,7 +8751,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D524">
-        <v>0.6368134021759033</v>
+        <v>1.033373713493347</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -8765,7 +8765,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D525">
-        <v>3.71944260597229</v>
+        <v>4.343436241149902</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -8779,7 +8779,7 @@
         <v>-9.199999809265137</v>
       </c>
       <c r="D526">
-        <v>2.301364183425903</v>
+        <v>2.30445122718811</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -8793,7 +8793,7 @@
         <v>-14</v>
       </c>
       <c r="D527">
-        <v>-11.18487644195557</v>
+        <v>-11.79249382019043</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -8807,7 +8807,7 @@
         <v>-12.89999961853027</v>
       </c>
       <c r="D528">
-        <v>-8.241159439086914</v>
+        <v>-10.76381969451904</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -8821,7 +8821,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D529">
-        <v>-2.056191205978394</v>
+        <v>-2.900289535522461</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -8835,7 +8835,7 @@
         <v>-3.5</v>
       </c>
       <c r="D530">
-        <v>-0.471246212720871</v>
+        <v>0.06154194474220276</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -8849,7 +8849,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D531">
-        <v>0.3642881810665131</v>
+        <v>0.7595840692520142</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -8863,7 +8863,7 @@
         <v>-12.39999961853027</v>
       </c>
       <c r="D532">
-        <v>-7.062918663024902</v>
+        <v>-9.110262870788574</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -8877,7 +8877,7 @@
         <v>-10.10000038146973</v>
       </c>
       <c r="D533">
-        <v>-3.320927619934082</v>
+        <v>-3.323974609375</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -8891,7 +8891,7 @@
         <v>-26</v>
       </c>
       <c r="D534">
-        <v>-16.23659324645996</v>
+        <v>-16.43742752075195</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -8905,7 +8905,7 @@
         <v>19.79999923706055</v>
       </c>
       <c r="D535">
-        <v>15.67385482788086</v>
+        <v>15.88788509368896</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -8919,7 +8919,7 @@
         <v>-2</v>
       </c>
       <c r="D536">
-        <v>0.3612911403179169</v>
+        <v>0.6177946329116821</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -8933,7 +8933,7 @@
         <v>-2.5</v>
       </c>
       <c r="D537">
-        <v>-3.196330308914185</v>
+        <v>-1.655475854873657</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -8947,7 +8947,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D538">
-        <v>1.150801062583923</v>
+        <v>0.5722538232803345</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -8961,7 +8961,7 @@
         <v>-7.800000190734863</v>
       </c>
       <c r="D539">
-        <v>-7.583199977874756</v>
+        <v>-7.08691930770874</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -8975,7 +8975,7 @@
         <v>-13</v>
       </c>
       <c r="D540">
-        <v>-14.50223255157471</v>
+        <v>-14.83175468444824</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -8989,7 +8989,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D541">
-        <v>2.445879220962524</v>
+        <v>2.225550889968872</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -9003,7 +9003,7 @@
         <v>-7.900000095367432</v>
       </c>
       <c r="D542">
-        <v>-5.300877571105957</v>
+        <v>-5.792953491210938</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -9017,7 +9017,7 @@
         <v>15.19999980926514</v>
       </c>
       <c r="D543">
-        <v>10.47270393371582</v>
+        <v>11.70144271850586</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -9031,7 +9031,7 @@
         <v>7</v>
       </c>
       <c r="D544">
-        <v>12.34314632415771</v>
+        <v>12.67321109771729</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -9045,7 +9045,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D545">
-        <v>0.1144932806491852</v>
+        <v>-0.2601555585861206</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -9059,7 +9059,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D546">
-        <v>-2.366519451141357</v>
+        <v>-0.2149164080619812</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -9073,7 +9073,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D547">
-        <v>-0.8488845825195312</v>
+        <v>-0.9668259620666504</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9087,7 +9087,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D548">
-        <v>-2.87622857093811</v>
+        <v>-4.195029735565186</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -9101,7 +9101,7 @@
         <v>-6.900000095367432</v>
       </c>
       <c r="D549">
-        <v>-1.360659599304199</v>
+        <v>-0.8292429447174072</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9115,7 +9115,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D550">
-        <v>-6.11824893951416</v>
+        <v>-9.228887557983398</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -9129,7 +9129,7 @@
         <v>-17.20000076293945</v>
       </c>
       <c r="D551">
-        <v>-11.57972049713135</v>
+        <v>-15.39368152618408</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -9143,7 +9143,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D552">
-        <v>-3.977487802505493</v>
+        <v>-4.035413265228271</v>
       </c>
     </row>
   </sheetData>
